--- a/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_R2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_R2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_R2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_R2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_R2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_R2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_R2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_R2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_R2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_R2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_R2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_R2</t>
         </is>
@@ -443,48 +448,51 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.4226732163016362</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.6138839211684494</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.6560003917844555</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.6763348182047245</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.7075797549612501</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.7169462343775983</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.736819128221714</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.7562501938920931</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.76129717022153</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.7675591744150942</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.7830358521120926</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.7904921357124712</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.8137724041543795</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.830437527315436</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.8417037666528494</v>
       </c>
     </row>
@@ -495,48 +503,51 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.5005860439610934</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.6329577775013353</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.6495964726922731</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.6993756497156882</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.7126751045868035</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.7413693517109444</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.7652751634870232</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.7825354032661584</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.801213664010606</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.8170582807549697</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.8414621102586555</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.8532896308971735</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.8773430706421189</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.8890925322691144</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.9007527255040253</v>
       </c>
     </row>
@@ -547,48 +558,51 @@
         </is>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>0.4435334755293588</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.600791091792698</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.6203175296441081</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.6502090492697123</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.6907959241636793</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.7195321711578067</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.732135750913034</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.7466196098126303</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.7705921354126433</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.7932698534804999</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.8027958470869203</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.8255327656170132</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.8393737670387228</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.848089418138862</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.8618835817022211</v>
       </c>
     </row>
@@ -599,48 +613,51 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>0.6100318168402478</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.6456035090591881</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.6635752452708878</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.6976069644309328</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.7251106964022684</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.7369106433437098</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.7444859076384371</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.7624378561161853</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.78760020111444</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.8059649867535625</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.830366778796621</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.8490138029684103</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.8650169818653041</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.8763531453168967</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.8882743931372074</v>
       </c>
     </row>
@@ -651,48 +668,51 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0.6070171617662247</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.6393045257378471</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.6610511929476248</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.7001481256441999</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.7246880100477294</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.7307487279863828</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.749984657749466</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.7661223764520513</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.780111668543195</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.7929170623352036</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.8099297843089326</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.8274049901785364</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.8482249877342345</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.8595225665143156</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.8731733790000817</v>
       </c>
     </row>
@@ -703,48 +723,51 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.4485490768089913</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.61201724408647</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.676416279468887</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.6880526294465205</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.7135555272214058</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.7202028579663428</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.7360009114323256</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.753229656421244</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.7705416090376991</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.783722773582618</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.8042615261658581</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.8234075120408724</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.8352283264744101</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.8483520578819547</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0.8581856967680425</v>
       </c>
     </row>
@@ -755,48 +778,51 @@
         </is>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>0.5206052769768158</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.6078732584528704</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.6768386823180945</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.7037229690604321</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.7121855486138966</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.7348135597008684</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.7427445006452336</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.7597145142683589</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.7746048816464201</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.789588720110749</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.8031058147400687</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.816693849482493</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.8268848490434663</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.8435914127577882</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0.8577375082572827</v>
       </c>
     </row>
@@ -807,48 +833,51 @@
         </is>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.5205623175890227</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.60784629969889</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.6766332412951904</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.7028171165111605</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.7100060660481193</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.7286237616018298</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.734203989890325</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.7416622158583425</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.7462717478579692</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.7541234170239347</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.7585244018577597</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.7646851494990351</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.7689951138495983</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.7761696970643259</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0.7800405819156587</v>
       </c>
     </row>
@@ -859,48 +888,51 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>0.5205230327394337</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.6078334575093147</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.6765871964360762</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.7027455658396173</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.7099420570343165</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.7284543386780953</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.7338969276303087</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.7410681466041162</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.745385805177039</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.7525764391054717</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.7564737602597286</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.7616680137893131</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.7655557673130832</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.772519523027285</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0.7766760465580256</v>
       </c>
     </row>
@@ -911,48 +943,51 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.5205642637601677</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.6078198436452922</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.6764687298641887</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.7026497284810076</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.7099242198630991</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.7288095526977996</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.7351042901912949</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.7448741713625877</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.7510992033293369</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.7589391668194596</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.7632262826815993</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.7686588052349057</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.7718341747693007</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.7779698825016332</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0.7807528906390273</v>
       </c>
     </row>
@@ -963,48 +998,51 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.6256684992605344</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.6630786191967493</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.6819965972183346</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.7147027132907793</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.7362379508688577</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.7469515443669583</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.7565681659873583</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.7683866818759123</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.7841498226811183</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.8009544486888206</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.8268471550639334</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.8406186594429166</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.8534902639285242</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.8644780794675748</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.8749142902315558</v>
       </c>
     </row>
@@ -1015,48 +1053,51 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.623600934933505</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.6724030165401826</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.7048940196226932</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.7262105491165037</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.7383713157551386</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.7631285723867025</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.7768540342483207</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.7916642318861681</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.8111424369511484</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.8292586947578544</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.838455531982401</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.8476495289339984</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.8552980048096673</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.8636449591608242</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.8705691232402755</v>
       </c>
     </row>
@@ -1067,48 +1108,51 @@
         </is>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>0.4485398169543739</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.6120047585857009</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.6763062763003131</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.6878703626195042</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.7128328963973657</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.7188079138014601</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.7321503554785089</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.7464360105776009</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.7575777158710986</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.7655713227924297</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.7732484260914736</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.7773295341039215</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.7824535508271264</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.7870817943225555</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.7927494725763725</v>
       </c>
     </row>
@@ -1119,48 +1163,51 @@
         </is>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>0.448511715328396</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.6120032947009737</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.6762586925598717</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.6878087637275889</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.712700239775986</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.7185632200713277</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.7313985817540859</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.7451195419212586</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.7551617992987796</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.7623327996823989</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.768741351489313</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.7727528621171182</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.7791242477083333</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.783352542439949</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0.7860256116781796</v>
       </c>
     </row>
@@ -1171,48 +1218,51 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>0.448476346110824</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.6119996016794711</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.6761995977983097</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.6877566283887291</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.7126973949292821</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.7185199001842656</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.7310524955354933</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.7442990558997337</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.7534807251128877</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.760408363610112</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.765723677635098</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.770422751839026</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.7763525053617326</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.7821635191024041</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.7850589466587238</v>
       </c>
     </row>
@@ -1223,48 +1273,51 @@
         </is>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>0.4483883977671762</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.6119913577504019</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.6760864073434152</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.6876694066214953</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.7127258522238242</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.7185493417264381</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.7308744008531578</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.7440946090728079</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.7525416934845811</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.7596468122731121</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.7642136766817194</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.7689700890305078</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.7735409597238408</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.7790692820746439</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.7817854829898545</v>
       </c>
     </row>
@@ -1275,48 +1328,51 @@
         </is>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>0.6254383605318308</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.6615932431008031</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.6803159302351702</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.7141598823445331</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.7359262614007329</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.7490036951458934</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.7548996462337879</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.7687696820856427</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.7851600933200761</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.8065791099999177</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.8337853679740084</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.8537398902986324</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.8695941886802027</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.8802843150270426</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.8906915769326352</v>
       </c>
     </row>
@@ -1327,48 +1383,51 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>0.6224919371108901</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.6569526195550701</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.6800145127323822</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.7165034068000445</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.7328083539668219</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.7496493698460083</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.7537754773242387</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.7681085013189776</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.7814253983096977</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.7960308910790488</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.8111325045249616</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.8255041231691379</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.8464922887994928</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.8601290595470664</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.8763064415308368</v>
       </c>
     </row>
@@ -1379,48 +1438,51 @@
         </is>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>0.6210910742831441</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.652308683871048</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.6890106574368681</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.7201519444868552</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.7271502225270039</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.7365979628652959</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.7417708681833041</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.7585368445752898</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.7672528962768913</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.7804805812174564</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.7933934279889968</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.8052069952171826</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.8128029480333711</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.8252811874362772</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0.8408514889068348</v>
       </c>
     </row>
@@ -1431,48 +1493,51 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>0.4998168181581377</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.6309499478194083</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.6473903684835799</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.7024265058158221</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.712791072219251</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.729866326392413</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.7532352813101333</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.7806191687085745</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.7994655046766843</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.8225420820690176</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.8438822741112624</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.8584961400551591</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.8809394737254775</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.8908000221854809</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.9011362193708056</v>
       </c>
     </row>
@@ -1483,48 +1548,51 @@
         </is>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>0.4985239285187345</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.6304023384182063</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.6456991833217144</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.7036636498679292</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.7159647422967884</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.7283842663457809</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.7572032707875759</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.7742680749506569</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.8005978862523466</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.8249564073981428</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.8477920301836672</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.8760459809096657</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.8865231969815063</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8941932170273209</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.9039007781150128</v>
       </c>
     </row>
@@ -1535,48 +1603,51 @@
         </is>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>0.6203813130959508</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.6311306728877625</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.6684970969902839</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.6722097472374784</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.7017561025895327</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.7431719140563344</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.7714812935442726</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.7921852391362674</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.815613428682767</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.842783184662832</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.8673403315813437</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.8845524947129213</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.89876866316934</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.9076164970125759</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0.9213825246937632</v>
       </c>
     </row>
@@ -1587,48 +1658,51 @@
         </is>
       </c>
       <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
         <v>0.1840918414492465</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>0.2960504438224756</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>0.3331064709610626</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>0.3522554499687848</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>0.448796537318462</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>0.4945557341305714</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>0.5383583603701118</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>0.5859889252922732</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>0.6273841213236733</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <v>0.6978681304657449</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>0.7475517844705932</v>
       </c>
-      <c r="M24">
+      <c r="N24">
         <v>0.7810429863820574</v>
       </c>
-      <c r="N24">
+      <c r="O24">
         <v>0.8316665098709184</v>
       </c>
-      <c r="O24">
+      <c r="P24">
         <v>0.8589469996322274</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>0.8783834613984668</v>
       </c>
     </row>
@@ -1639,48 +1713,51 @@
         </is>
       </c>
       <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
         <v>0.1764488654759132</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>0.2644027471247471</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>0.3146907346351293</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>0.4236693634981171</v>
       </c>
-      <c r="F25">
+      <c r="G25">
         <v>0.4941362920425052</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>0.5426256033104866</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>0.5857364238976076</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>0.6043270915933251</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <v>0.6475451318766152</v>
       </c>
-      <c r="K25">
+      <c r="L25">
         <v>0.6836971900583453</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>0.7242586714127761</v>
       </c>
-      <c r="M25">
+      <c r="N25">
         <v>0.7753843582252604</v>
       </c>
-      <c r="N25">
+      <c r="O25">
         <v>0.8094660203685586</v>
       </c>
-      <c r="O25">
+      <c r="P25">
         <v>0.8400112497732125</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>0.8701850290549802</v>
       </c>
     </row>
@@ -1691,48 +1768,51 @@
         </is>
       </c>
       <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
         <v>0.1604150203944956</v>
       </c>
-      <c r="C26">
+      <c r="D26">
         <v>0.2408939514957437</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>0.2746094803883211</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>0.3188389358435878</v>
       </c>
-      <c r="F26">
+      <c r="G26">
         <v>0.3686311228853993</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>0.4056564089881269</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>0.4531556619104853</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>0.4698415987385348</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <v>0.5210509287913174</v>
       </c>
-      <c r="K26">
+      <c r="L26">
         <v>0.5524779609072408</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>0.5963079977418986</v>
       </c>
-      <c r="M26">
+      <c r="N26">
         <v>0.6259487813599758</v>
       </c>
-      <c r="N26">
+      <c r="O26">
         <v>0.6602953037389492</v>
       </c>
-      <c r="O26">
+      <c r="P26">
         <v>0.6753637680398795</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>0.7035492702268583</v>
       </c>
     </row>
@@ -1743,48 +1823,51 @@
         </is>
       </c>
       <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
         <v>0.1379680581024288</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>0.202694249326441</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>0.3498399196937682</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>0.3609043174902683</v>
       </c>
-      <c r="F27">
+      <c r="G27">
         <v>0.4055674112136565</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>0.4557667135259407</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>0.5039462758911726</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>0.5830668049837929</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>0.6181698242421869</v>
       </c>
-      <c r="K27">
+      <c r="L27">
         <v>0.6376281365074348</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>0.6468968708226034</v>
       </c>
-      <c r="M27">
+      <c r="N27">
         <v>0.6941639309733598</v>
       </c>
-      <c r="N27">
+      <c r="O27">
         <v>0.7179383098164724</v>
       </c>
-      <c r="O27">
+      <c r="P27">
         <v>0.7528780780930042</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>0.7718787965699969</v>
       </c>
     </row>
@@ -1795,48 +1878,51 @@
         </is>
       </c>
       <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
         <v>0.614293658835778</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>0.6579530093224538</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>0.6786271129734901</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>0.6848071581086843</v>
       </c>
-      <c r="F28">
+      <c r="G28">
         <v>0.6959954095143736</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>0.7129194161128041</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>0.7221748618644271</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>0.7783328774450973</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>0.8127068975113949</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <v>0.8383391899263134</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>0.8636918438811174</v>
       </c>
-      <c r="M28">
+      <c r="N28">
         <v>0.8915462502703473</v>
       </c>
-      <c r="N28">
+      <c r="O28">
         <v>0.9021152091386175</v>
       </c>
-      <c r="O28">
+      <c r="P28">
         <v>0.9152495330703383</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>0.928462629866889</v>
       </c>
     </row>
@@ -1847,48 +1933,51 @@
         </is>
       </c>
       <c r="B29">
+        <v>0</v>
+      </c>
+      <c r="C29">
         <v>0.6181119563074844</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>0.6612598818690909</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>0.6845441378969188</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>0.689906399203346</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <v>0.6985594922472322</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>0.7176185594169233</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>0.7251891423444052</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>0.7836483357880547</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>0.7971968629236641</v>
       </c>
-      <c r="K29">
+      <c r="L29">
         <v>0.8286904476556984</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>0.8467960573097729</v>
       </c>
-      <c r="M29">
+      <c r="N29">
         <v>0.8754871832530274</v>
       </c>
-      <c r="N29">
+      <c r="O29">
         <v>0.8975799559938856</v>
       </c>
-      <c r="O29">
+      <c r="P29">
         <v>0.9053066278574506</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>0.9201168820736503</v>
       </c>
     </row>
@@ -1899,48 +1988,51 @@
         </is>
       </c>
       <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
         <v>0.643643059036058</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>0.6607478569503746</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>0.6824024175880773</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>0.694668234845035</v>
       </c>
-      <c r="F30">
+      <c r="G30">
         <v>0.7038283457352166</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <v>0.7157744390010624</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>0.7374059753172015</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>0.7857617118363971</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>0.8241709802787103</v>
       </c>
-      <c r="K30">
+      <c r="L30">
         <v>0.8492042828109301</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>0.8771257292440526</v>
       </c>
-      <c r="M30">
+      <c r="N30">
         <v>0.8953398359376862</v>
       </c>
-      <c r="N30">
+      <c r="O30">
         <v>0.9094359937522729</v>
       </c>
-      <c r="O30">
+      <c r="P30">
         <v>0.9196243994109886</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>0.9333125664937219</v>
       </c>
     </row>
@@ -1951,48 +2043,51 @@
         </is>
       </c>
       <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
         <v>0.6435691565508974</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>0.6605499431309139</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>0.6812871811312768</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>0.6925218906424037</v>
       </c>
-      <c r="F31">
+      <c r="G31">
         <v>0.7000037964908183</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <v>0.7074864729925403</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>0.7167442989824901</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>0.7392307037361072</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>0.7585286140299142</v>
       </c>
-      <c r="K31">
+      <c r="L31">
         <v>0.7734864733688631</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>0.7816578468911607</v>
       </c>
-      <c r="M31">
+      <c r="N31">
         <v>0.7967872486406814</v>
       </c>
-      <c r="N31">
+      <c r="O31">
         <v>0.8089131261226953</v>
       </c>
-      <c r="O31">
+      <c r="P31">
         <v>0.8116973613255045</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>0.8267956429844036</v>
       </c>
     </row>
@@ -2003,48 +2098,51 @@
         </is>
       </c>
       <c r="B32">
+        <v>0</v>
+      </c>
+      <c r="C32">
         <v>0.6179891865896963</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>0.6611152238378326</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>0.6836626028756381</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>0.6887345541958698</v>
       </c>
-      <c r="F32">
+      <c r="G32">
         <v>0.6960480111656706</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <v>0.7062118776724273</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>0.709713034817502</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>0.7363622836172203</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>0.7427841844724516</v>
       </c>
-      <c r="K32">
+      <c r="L32">
         <v>0.757822860353172</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>0.7662494642028771</v>
       </c>
-      <c r="M32">
+      <c r="N32">
         <v>0.7767167953365317</v>
       </c>
-      <c r="N32">
+      <c r="O32">
         <v>0.7866994273157979</v>
       </c>
-      <c r="O32">
+      <c r="P32">
         <v>0.7921250303626941</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>0.8076328324146124</v>
       </c>
     </row>
@@ -2055,48 +2153,51 @@
         </is>
       </c>
       <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
         <v>0.6178848867318328</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>0.6610786094462839</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>0.6834860611700893</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>0.6885893400912492</v>
       </c>
-      <c r="F33">
+      <c r="G33">
         <v>0.695833622446561</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <v>0.7055925712205507</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>0.7089411430829455</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>0.7349364769389461</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <v>0.7415074642921033</v>
       </c>
-      <c r="K33">
+      <c r="L33">
         <v>0.7568542498303981</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>0.7649157545725253</v>
       </c>
-      <c r="M33">
+      <c r="N33">
         <v>0.7749173248090728</v>
       </c>
-      <c r="N33">
+      <c r="O33">
         <v>0.7835198925039324</v>
       </c>
-      <c r="O33">
+      <c r="P33">
         <v>0.7882716410613257</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>0.8009491368097972</v>
       </c>
     </row>
@@ -2107,48 +2208,51 @@
         </is>
       </c>
       <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
         <v>0.6178146309984232</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>0.6610574173285608</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <v>0.6833779493554066</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <v>0.6885050392337422</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <v>0.6957169276824462</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <v>0.7052657659617585</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>0.708541238120582</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>0.7341999190195752</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>0.7408773663386967</v>
       </c>
-      <c r="K34">
+      <c r="L34">
         <v>0.7565936723959916</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>0.7646208076536372</v>
       </c>
-      <c r="M34">
+      <c r="N34">
         <v>0.7744324548962728</v>
       </c>
-      <c r="N34">
+      <c r="O34">
         <v>0.7826804810354266</v>
       </c>
-      <c r="O34">
+      <c r="P34">
         <v>0.7873159526512181</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>0.7980438149125544</v>
       </c>
     </row>
@@ -2159,48 +2263,51 @@
         </is>
       </c>
       <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
         <v>0.6176325889485793</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>0.6609981323144348</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>0.6831351137334064</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>0.6883233221319154</v>
       </c>
-      <c r="F35">
+      <c r="G35">
         <v>0.6954741708434762</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <v>0.7044678160203042</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>0.707510463727157</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>0.7315454497338227</v>
       </c>
-      <c r="J35">
+      <c r="K35">
         <v>0.7382764610092023</v>
       </c>
-      <c r="K35">
+      <c r="L35">
         <v>0.7541596523540838</v>
       </c>
-      <c r="L35">
+      <c r="M35">
         <v>0.7622905377148462</v>
       </c>
-      <c r="M35">
+      <c r="N35">
         <v>0.7709882594654982</v>
       </c>
-      <c r="N35">
+      <c r="O35">
         <v>0.7778701055902639</v>
       </c>
-      <c r="O35">
+      <c r="P35">
         <v>0.7818142748581243</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>0.7889477468538194</v>
       </c>
     </row>
@@ -2211,48 +2318,51 @@
         </is>
       </c>
       <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
         <v>0.6180798884888821</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>0.661174442282767</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>0.6838510955361977</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>0.6889228491124338</v>
       </c>
-      <c r="F36">
+      <c r="G36">
         <v>0.6964035925163539</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <v>0.7077767500089767</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>0.7118187606643449</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>0.7431808669189185</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>0.7503701524050619</v>
       </c>
-      <c r="K36">
+      <c r="L36">
         <v>0.7673365562319682</v>
       </c>
-      <c r="L36">
+      <c r="M36">
         <v>0.7781592678344087</v>
       </c>
-      <c r="M36">
+      <c r="N36">
         <v>0.7945010048580714</v>
       </c>
-      <c r="N36">
+      <c r="O36">
         <v>0.8112410023459448</v>
       </c>
-      <c r="O36">
+      <c r="P36">
         <v>0.817506386068773</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>0.8312356677261645</v>
       </c>
     </row>
@@ -2263,48 +2373,51 @@
         </is>
       </c>
       <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
         <v>0.6180592335406229</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>0.66116444829425</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>0.6838012519195112</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>0.6888709840074104</v>
       </c>
-      <c r="F37">
+      <c r="G37">
         <v>0.6963204791949642</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <v>0.7074913603255171</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>0.7114491513952791</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>0.7423612951787404</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>0.7495453886269636</v>
       </c>
-      <c r="K37">
+      <c r="L37">
         <v>0.7665749868376014</v>
       </c>
-      <c r="L37">
+      <c r="M37">
         <v>0.7772216719199205</v>
       </c>
-      <c r="M37">
+      <c r="N37">
         <v>0.7937793159931373</v>
       </c>
-      <c r="N37">
+      <c r="O37">
         <v>0.8104287431268917</v>
       </c>
-      <c r="O37">
+      <c r="P37">
         <v>0.8167861382579822</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>0.8308019003483891</v>
       </c>
     </row>
@@ -2315,48 +2428,51 @@
         </is>
       </c>
       <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
         <v>0.6180310735987883</v>
       </c>
-      <c r="C38">
+      <c r="D38">
         <v>0.6611521097597738</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <v>0.6837308856743245</v>
       </c>
-      <c r="E38">
+      <c r="F38">
         <v>0.6888038109726343</v>
       </c>
-      <c r="F38">
+      <c r="G38">
         <v>0.6962044028996262</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <v>0.7070722927604218</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>0.7108927045641135</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>0.7408014526744857</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>0.7477674868031832</v>
       </c>
-      <c r="K38">
+      <c r="L38">
         <v>0.7637391426381358</v>
       </c>
-      <c r="L38">
+      <c r="M38">
         <v>0.7734920332965789</v>
       </c>
-      <c r="M38">
+      <c r="N38">
         <v>0.7884367946622814</v>
       </c>
-      <c r="N38">
+      <c r="O38">
         <v>0.804048843885897</v>
       </c>
-      <c r="O38">
+      <c r="P38">
         <v>0.8098402207905973</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>0.8236718459068502</v>
       </c>
     </row>
@@ -2367,48 +2483,51 @@
         </is>
       </c>
       <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
         <v>0.617995194249328</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>0.6611417899323763</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>0.6836410818050516</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>0.6887230346077483</v>
       </c>
-      <c r="F39">
+      <c r="G39">
         <v>0.6960749758000186</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <v>0.7066742281563816</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>0.7103690221384849</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>0.7394452486860534</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>0.7462042379762602</v>
       </c>
-      <c r="K39">
+      <c r="L39">
         <v>0.7612108448963886</v>
       </c>
-      <c r="L39">
+      <c r="M39">
         <v>0.770039119328475</v>
       </c>
-      <c r="M39">
+      <c r="N39">
         <v>0.7832830265259871</v>
       </c>
-      <c r="N39">
+      <c r="O39">
         <v>0.7965826135905658</v>
       </c>
-      <c r="O39">
+      <c r="P39">
         <v>0.8013718017417313</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>0.8119303040251304</v>
       </c>
     </row>
@@ -2419,48 +2538,51 @@
         </is>
       </c>
       <c r="B40">
+        <v>0</v>
+      </c>
+      <c r="C40">
         <v>0.6176374428783138</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>0.6610309869644317</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>0.6830410955684432</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>0.6882641874686758</v>
       </c>
-      <c r="F40">
+      <c r="G40">
         <v>0.6954382226243554</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <v>0.704601317694082</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>0.7076719493595529</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>0.7328392466161948</v>
       </c>
-      <c r="J40">
+      <c r="K40">
         <v>0.7398914845152426</v>
       </c>
-      <c r="K40">
+      <c r="L40">
         <v>0.7553611808501715</v>
       </c>
-      <c r="L40">
+      <c r="M40">
         <v>0.7629851017662035</v>
       </c>
-      <c r="M40">
+      <c r="N40">
         <v>0.7734014676482637</v>
       </c>
-      <c r="N40">
+      <c r="O40">
         <v>0.7810384565266301</v>
       </c>
-      <c r="O40">
+      <c r="P40">
         <v>0.784842566190218</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>0.7916868678540425</v>
       </c>
     </row>
@@ -2471,48 +2593,51 @@
         </is>
       </c>
       <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
         <v>0.6491293981171593</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>0.6726938100643867</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>0.7138724559852694</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>0.7330735681796979</v>
       </c>
-      <c r="F41">
+      <c r="G41">
         <v>0.7641145701796569</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <v>0.8050135970665708</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>0.8312799512450997</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>0.844798996076043</v>
       </c>
-      <c r="J41">
+      <c r="K41">
         <v>0.8552680924950157</v>
       </c>
-      <c r="K41">
+      <c r="L41">
         <v>0.867386202617997</v>
       </c>
-      <c r="L41">
+      <c r="M41">
         <v>0.8786659602863093</v>
       </c>
-      <c r="M41">
+      <c r="N41">
         <v>0.8873752875208518</v>
       </c>
-      <c r="N41">
+      <c r="O41">
         <v>0.9006802935262573</v>
       </c>
-      <c r="O41">
+      <c r="P41">
         <v>0.9084155037317208</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>0.9158862420280217</v>
       </c>
     </row>
@@ -2523,48 +2648,51 @@
         </is>
       </c>
       <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
         <v>0.6472802226904981</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>0.6663741688953713</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>0.697702230969182</v>
       </c>
-      <c r="E42">
+      <c r="F42">
         <v>0.7109358571589171</v>
       </c>
-      <c r="F42">
+      <c r="G42">
         <v>0.723360917531636</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <v>0.7396261355081913</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>0.7539983296425135</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>0.7792358700064386</v>
       </c>
-      <c r="J42">
+      <c r="K42">
         <v>0.7947521245689063</v>
       </c>
-      <c r="K42">
+      <c r="L42">
         <v>0.8287249317479332</v>
       </c>
-      <c r="L42">
+      <c r="M42">
         <v>0.849121666411473</v>
       </c>
-      <c r="M42">
+      <c r="N42">
         <v>0.8530308527280686</v>
       </c>
-      <c r="N42">
+      <c r="O42">
         <v>0.8677731712103081</v>
       </c>
-      <c r="O42">
+      <c r="P42">
         <v>0.8766867149564259</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>0.8833651244186799</v>
       </c>
     </row>
@@ -2575,48 +2703,51 @@
         </is>
       </c>
       <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
         <v>0.6472287373179957</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>0.6662561930641608</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>0.6951197036800285</v>
       </c>
-      <c r="E43">
+      <c r="F43">
         <v>0.7082661397085106</v>
       </c>
-      <c r="F43">
+      <c r="G43">
         <v>0.7204592489087327</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <v>0.7364241948925039</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>0.7469732062341955</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>0.7646449185916887</v>
       </c>
-      <c r="J43">
+      <c r="K43">
         <v>0.7802541028556874</v>
       </c>
-      <c r="K43">
+      <c r="L43">
         <v>0.8000112483524892</v>
       </c>
-      <c r="L43">
+      <c r="M43">
         <v>0.80700683213346</v>
       </c>
-      <c r="M43">
+      <c r="N43">
         <v>0.827274343004009</v>
       </c>
-      <c r="N43">
+      <c r="O43">
         <v>0.8401025460734068</v>
       </c>
-      <c r="O43">
+      <c r="P43">
         <v>0.848624980571242</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>0.8612558416679517</v>
       </c>
     </row>
@@ -2627,48 +2758,51 @@
         </is>
       </c>
       <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
         <v>0.619735203434455</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>0.6333832928066546</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <v>0.6787383133515561</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>0.7124562340646758</v>
       </c>
-      <c r="F44">
+      <c r="G44">
         <v>0.7496361943136062</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <v>0.7695284008053538</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>0.7976390916157918</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>0.8204771615311517</v>
       </c>
-      <c r="J44">
+      <c r="K44">
         <v>0.8370226248867162</v>
       </c>
-      <c r="K44">
+      <c r="L44">
         <v>0.848164293111459</v>
       </c>
-      <c r="L44">
+      <c r="M44">
         <v>0.8611226525745019</v>
       </c>
-      <c r="M44">
+      <c r="N44">
         <v>0.874107463704207</v>
       </c>
-      <c r="N44">
+      <c r="O44">
         <v>0.8878957158863929</v>
       </c>
-      <c r="O44">
+      <c r="P44">
         <v>0.8982594701310169</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>0.9086657345150582</v>
       </c>
     </row>
@@ -2679,48 +2813,51 @@
         </is>
       </c>
       <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
         <v>0.6173773223053315</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>0.6628752012978114</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <v>0.7229838463206135</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>0.7601420134698175</v>
       </c>
-      <c r="F45">
+      <c r="G45">
         <v>0.7912858450045748</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <v>0.8183358407599028</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>0.8360150271944462</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>0.8472208098695676</v>
       </c>
-      <c r="J45">
+      <c r="K45">
         <v>0.8625139580719926</v>
       </c>
-      <c r="K45">
+      <c r="L45">
         <v>0.8700905091512906</v>
       </c>
-      <c r="L45">
+      <c r="M45">
         <v>0.888471474998785</v>
       </c>
-      <c r="M45">
+      <c r="N45">
         <v>0.9070302450830061</v>
       </c>
-      <c r="N45">
+      <c r="O45">
         <v>0.9182267021434549</v>
       </c>
-      <c r="O45">
+      <c r="P45">
         <v>0.9278150153230389</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>0.9365466625774925</v>
       </c>
     </row>
@@ -2731,48 +2868,51 @@
         </is>
       </c>
       <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
         <v>0.5038544743145424</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>0.6511762017213585</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>0.6744938819741688</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>0.7216140036739931</v>
       </c>
-      <c r="F46">
+      <c r="G46">
         <v>0.751146005814281</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <v>0.7658088206510554</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>0.7826458849980422</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>0.7947978155069327</v>
       </c>
-      <c r="J46">
+      <c r="K46">
         <v>0.8287876589326277</v>
       </c>
-      <c r="K46">
+      <c r="L46">
         <v>0.8484811224511225</v>
       </c>
-      <c r="L46">
+      <c r="M46">
         <v>0.864581405783565</v>
       </c>
-      <c r="M46">
+      <c r="N46">
         <v>0.8933271136131946</v>
       </c>
-      <c r="N46">
+      <c r="O46">
         <v>0.9007914603296567</v>
       </c>
-      <c r="O46">
+      <c r="P46">
         <v>0.9094671571744516</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>0.9226142305883073</v>
       </c>
     </row>
@@ -2783,48 +2923,51 @@
         </is>
       </c>
       <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
         <v>0.6355865009659161</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>0.669414599609491</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>0.7030182470801745</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>0.7259403648356724</v>
       </c>
-      <c r="F47">
+      <c r="G47">
         <v>0.7571791451578468</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <v>0.7788414061450253</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>0.8037869263306345</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>0.8175071837806387</v>
       </c>
-      <c r="J47">
+      <c r="K47">
         <v>0.8386567458185377</v>
       </c>
-      <c r="K47">
+      <c r="L47">
         <v>0.8669944780684178</v>
       </c>
-      <c r="L47">
+      <c r="M47">
         <v>0.883769512092448</v>
       </c>
-      <c r="M47">
+      <c r="N47">
         <v>0.8975871751366885</v>
       </c>
-      <c r="N47">
+      <c r="O47">
         <v>0.9090488446200516</v>
       </c>
-      <c r="O47">
+      <c r="P47">
         <v>0.9204252326123947</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>0.9274162461382027</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/X13.cis.beta.carotene/Resultats_X13.cis.beta.carotene_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1654,1320 +1654,1100 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0.1840918414492465</v>
+        <v>0.614293658835778</v>
       </c>
       <c r="D24">
-        <v>0.2960504438224756</v>
+        <v>0.6579530093224538</v>
       </c>
       <c r="E24">
-        <v>0.3331064709610626</v>
+        <v>0.6786271129734901</v>
       </c>
       <c r="F24">
-        <v>0.3522554499687848</v>
+        <v>0.6848071581086843</v>
       </c>
       <c r="G24">
-        <v>0.448796537318462</v>
+        <v>0.6959954095143736</v>
       </c>
       <c r="H24">
-        <v>0.4945557341305714</v>
+        <v>0.7129194161128041</v>
       </c>
       <c r="I24">
-        <v>0.5383583603701118</v>
+        <v>0.7221748618644271</v>
       </c>
       <c r="J24">
-        <v>0.5859889252922732</v>
+        <v>0.7783328774450973</v>
       </c>
       <c r="K24">
-        <v>0.6273841213236733</v>
+        <v>0.8127068975113949</v>
       </c>
       <c r="L24">
-        <v>0.6978681304657449</v>
+        <v>0.8383391899263134</v>
       </c>
       <c r="M24">
-        <v>0.7475517844705932</v>
+        <v>0.8636918438811174</v>
       </c>
       <c r="N24">
-        <v>0.7810429863820574</v>
+        <v>0.8915462502703473</v>
       </c>
       <c r="O24">
-        <v>0.8316665098709184</v>
+        <v>0.9021152091386175</v>
       </c>
       <c r="P24">
-        <v>0.8589469996322274</v>
+        <v>0.9152495330703383</v>
       </c>
       <c r="Q24">
-        <v>0.8783834613984668</v>
+        <v>0.928462629866889</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0.1764488654759132</v>
+        <v>0.6181119563074844</v>
       </c>
       <c r="D25">
-        <v>0.2644027471247471</v>
+        <v>0.6612598818690909</v>
       </c>
       <c r="E25">
-        <v>0.3146907346351293</v>
+        <v>0.6845441378969188</v>
       </c>
       <c r="F25">
-        <v>0.4236693634981171</v>
+        <v>0.689906399203346</v>
       </c>
       <c r="G25">
-        <v>0.4941362920425052</v>
+        <v>0.6985594922472322</v>
       </c>
       <c r="H25">
-        <v>0.5426256033104866</v>
+        <v>0.7176185594169233</v>
       </c>
       <c r="I25">
-        <v>0.5857364238976076</v>
+        <v>0.7251891423444052</v>
       </c>
       <c r="J25">
-        <v>0.6043270915933251</v>
+        <v>0.7836483357880547</v>
       </c>
       <c r="K25">
-        <v>0.6475451318766152</v>
+        <v>0.7971968629236641</v>
       </c>
       <c r="L25">
-        <v>0.6836971900583453</v>
+        <v>0.8286904476556984</v>
       </c>
       <c r="M25">
-        <v>0.7242586714127761</v>
+        <v>0.8467960573097729</v>
       </c>
       <c r="N25">
-        <v>0.7753843582252604</v>
+        <v>0.8754871832530274</v>
       </c>
       <c r="O25">
-        <v>0.8094660203685586</v>
+        <v>0.8975799559938856</v>
       </c>
       <c r="P25">
-        <v>0.8400112497732125</v>
+        <v>0.9053066278574506</v>
       </c>
       <c r="Q25">
-        <v>0.8701850290549802</v>
+        <v>0.9201168820736503</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0.1604150203944956</v>
+        <v>0.643643059036058</v>
       </c>
       <c r="D26">
-        <v>0.2408939514957437</v>
+        <v>0.6607478569503746</v>
       </c>
       <c r="E26">
-        <v>0.2746094803883211</v>
+        <v>0.6824024175880773</v>
       </c>
       <c r="F26">
-        <v>0.3188389358435878</v>
+        <v>0.694668234845035</v>
       </c>
       <c r="G26">
-        <v>0.3686311228853993</v>
+        <v>0.7038283457352166</v>
       </c>
       <c r="H26">
-        <v>0.4056564089881269</v>
+        <v>0.7157744390010624</v>
       </c>
       <c r="I26">
-        <v>0.4531556619104853</v>
+        <v>0.7374059753172015</v>
       </c>
       <c r="J26">
-        <v>0.4698415987385348</v>
+        <v>0.7857617118363971</v>
       </c>
       <c r="K26">
-        <v>0.5210509287913174</v>
+        <v>0.8241709802787103</v>
       </c>
       <c r="L26">
-        <v>0.5524779609072408</v>
+        <v>0.8492042828109301</v>
       </c>
       <c r="M26">
-        <v>0.5963079977418986</v>
+        <v>0.8771257292440526</v>
       </c>
       <c r="N26">
-        <v>0.6259487813599758</v>
+        <v>0.8953398359376862</v>
       </c>
       <c r="O26">
-        <v>0.6602953037389492</v>
+        <v>0.9094359937522729</v>
       </c>
       <c r="P26">
-        <v>0.6753637680398795</v>
+        <v>0.9196243994109886</v>
       </c>
       <c r="Q26">
-        <v>0.7035492702268583</v>
+        <v>0.9333125664937219</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.1379680581024288</v>
+        <v>0.6435691565508974</v>
       </c>
       <c r="D27">
-        <v>0.202694249326441</v>
+        <v>0.6605499431309139</v>
       </c>
       <c r="E27">
-        <v>0.3498399196937682</v>
+        <v>0.6812871811312768</v>
       </c>
       <c r="F27">
-        <v>0.3609043174902683</v>
+        <v>0.6925218906424037</v>
       </c>
       <c r="G27">
-        <v>0.4055674112136565</v>
+        <v>0.7000037964908183</v>
       </c>
       <c r="H27">
-        <v>0.4557667135259407</v>
+        <v>0.7074864729925403</v>
       </c>
       <c r="I27">
-        <v>0.5039462758911726</v>
+        <v>0.7167442989824901</v>
       </c>
       <c r="J27">
-        <v>0.5830668049837929</v>
+        <v>0.7392307037361072</v>
       </c>
       <c r="K27">
-        <v>0.6181698242421869</v>
+        <v>0.7585286140299142</v>
       </c>
       <c r="L27">
-        <v>0.6376281365074348</v>
+        <v>0.7734864733688631</v>
       </c>
       <c r="M27">
-        <v>0.6468968708226034</v>
+        <v>0.7816578468911607</v>
       </c>
       <c r="N27">
-        <v>0.6941639309733598</v>
+        <v>0.7967872486406814</v>
       </c>
       <c r="O27">
-        <v>0.7179383098164724</v>
+        <v>0.8089131261226953</v>
       </c>
       <c r="P27">
-        <v>0.7528780780930042</v>
+        <v>0.8116973613255045</v>
       </c>
       <c r="Q27">
-        <v>0.7718787965699969</v>
+        <v>0.8267956429844036</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0.614293658835778</v>
+        <v>0.6179891865896963</v>
       </c>
       <c r="D28">
-        <v>0.6579530093224538</v>
+        <v>0.6611152238378326</v>
       </c>
       <c r="E28">
-        <v>0.6786271129734901</v>
+        <v>0.6836626028756381</v>
       </c>
       <c r="F28">
-        <v>0.6848071581086843</v>
+        <v>0.6887345541958698</v>
       </c>
       <c r="G28">
-        <v>0.6959954095143736</v>
+        <v>0.6960480111656706</v>
       </c>
       <c r="H28">
-        <v>0.7129194161128041</v>
+        <v>0.7062118776724273</v>
       </c>
       <c r="I28">
-        <v>0.7221748618644271</v>
+        <v>0.709713034817502</v>
       </c>
       <c r="J28">
-        <v>0.7783328774450973</v>
+        <v>0.7363622836172203</v>
       </c>
       <c r="K28">
-        <v>0.8127068975113949</v>
+        <v>0.7427841844724516</v>
       </c>
       <c r="L28">
-        <v>0.8383391899263134</v>
+        <v>0.757822860353172</v>
       </c>
       <c r="M28">
-        <v>0.8636918438811174</v>
+        <v>0.7662494642028771</v>
       </c>
       <c r="N28">
-        <v>0.8915462502703473</v>
+        <v>0.7767167953365317</v>
       </c>
       <c r="O28">
-        <v>0.9021152091386175</v>
+        <v>0.7866994273157979</v>
       </c>
       <c r="P28">
-        <v>0.9152495330703383</v>
+        <v>0.7921250303626941</v>
       </c>
       <c r="Q28">
-        <v>0.928462629866889</v>
+        <v>0.8076328324146124</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
         <v>0</v>
       </c>
       <c r="C29">
-        <v>0.6181119563074844</v>
+        <v>0.6178848867318328</v>
       </c>
       <c r="D29">
-        <v>0.6612598818690909</v>
+        <v>0.6610786094462839</v>
       </c>
       <c r="E29">
-        <v>0.6845441378969188</v>
+        <v>0.6834860611700893</v>
       </c>
       <c r="F29">
-        <v>0.689906399203346</v>
+        <v>0.6885893400912492</v>
       </c>
       <c r="G29">
-        <v>0.6985594922472322</v>
+        <v>0.695833622446561</v>
       </c>
       <c r="H29">
-        <v>0.7176185594169233</v>
+        <v>0.7055925712205507</v>
       </c>
       <c r="I29">
-        <v>0.7251891423444052</v>
+        <v>0.7089411430829455</v>
       </c>
       <c r="J29">
-        <v>0.7836483357880547</v>
+        <v>0.7349364769389461</v>
       </c>
       <c r="K29">
-        <v>0.7971968629236641</v>
+        <v>0.7415074642921033</v>
       </c>
       <c r="L29">
-        <v>0.8286904476556984</v>
+        <v>0.7568542498303981</v>
       </c>
       <c r="M29">
-        <v>0.8467960573097729</v>
+        <v>0.7649157545725253</v>
       </c>
       <c r="N29">
-        <v>0.8754871832530274</v>
+        <v>0.7749173248090728</v>
       </c>
       <c r="O29">
-        <v>0.8975799559938856</v>
+        <v>0.7835198925039324</v>
       </c>
       <c r="P29">
-        <v>0.9053066278574506</v>
+        <v>0.7882716410613257</v>
       </c>
       <c r="Q29">
-        <v>0.9201168820736503</v>
+        <v>0.8009491368097972</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.643643059036058</v>
+        <v>0.6178146309984232</v>
       </c>
       <c r="D30">
-        <v>0.6607478569503746</v>
+        <v>0.6610574173285608</v>
       </c>
       <c r="E30">
-        <v>0.6824024175880773</v>
+        <v>0.6833779493554066</v>
       </c>
       <c r="F30">
-        <v>0.694668234845035</v>
+        <v>0.6885050392337422</v>
       </c>
       <c r="G30">
-        <v>0.7038283457352166</v>
+        <v>0.6957169276824462</v>
       </c>
       <c r="H30">
-        <v>0.7157744390010624</v>
+        <v>0.7052657659617585</v>
       </c>
       <c r="I30">
-        <v>0.7374059753172015</v>
+        <v>0.708541238120582</v>
       </c>
       <c r="J30">
-        <v>0.7857617118363971</v>
+        <v>0.7341999190195752</v>
       </c>
       <c r="K30">
-        <v>0.8241709802787103</v>
+        <v>0.7408773663386967</v>
       </c>
       <c r="L30">
-        <v>0.8492042828109301</v>
+        <v>0.7565936723959916</v>
       </c>
       <c r="M30">
-        <v>0.8771257292440526</v>
+        <v>0.7646208076536372</v>
       </c>
       <c r="N30">
-        <v>0.8953398359376862</v>
+        <v>0.7744324548962728</v>
       </c>
       <c r="O30">
-        <v>0.9094359937522729</v>
+        <v>0.7826804810354266</v>
       </c>
       <c r="P30">
-        <v>0.9196243994109886</v>
+        <v>0.7873159526512181</v>
       </c>
       <c r="Q30">
-        <v>0.9333125664937219</v>
+        <v>0.7980438149125544</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0.6435691565508974</v>
+        <v>0.6176325889485793</v>
       </c>
       <c r="D31">
-        <v>0.6605499431309139</v>
+        <v>0.6609981323144348</v>
       </c>
       <c r="E31">
-        <v>0.6812871811312768</v>
+        <v>0.6831351137334064</v>
       </c>
       <c r="F31">
-        <v>0.6925218906424037</v>
+        <v>0.6883233221319154</v>
       </c>
       <c r="G31">
-        <v>0.7000037964908183</v>
+        <v>0.6954741708434762</v>
       </c>
       <c r="H31">
-        <v>0.7074864729925403</v>
+        <v>0.7044678160203042</v>
       </c>
       <c r="I31">
-        <v>0.7167442989824901</v>
+        <v>0.707510463727157</v>
       </c>
       <c r="J31">
-        <v>0.7392307037361072</v>
+        <v>0.7315454497338227</v>
       </c>
       <c r="K31">
-        <v>0.7585286140299142</v>
+        <v>0.7382764610092023</v>
       </c>
       <c r="L31">
-        <v>0.7734864733688631</v>
+        <v>0.7541596523540838</v>
       </c>
       <c r="M31">
-        <v>0.7816578468911607</v>
+        <v>0.7622905377148462</v>
       </c>
       <c r="N31">
-        <v>0.7967872486406814</v>
+        <v>0.7709882594654982</v>
       </c>
       <c r="O31">
-        <v>0.8089131261226953</v>
+        <v>0.7778701055902639</v>
       </c>
       <c r="P31">
-        <v>0.8116973613255045</v>
+        <v>0.7818142748581243</v>
       </c>
       <c r="Q31">
-        <v>0.8267956429844036</v>
+        <v>0.7889477468538194</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0.6179891865896963</v>
+        <v>0.6180798884888821</v>
       </c>
       <c r="D32">
-        <v>0.6611152238378326</v>
+        <v>0.661174442282767</v>
       </c>
       <c r="E32">
-        <v>0.6836626028756381</v>
+        <v>0.6838510955361977</v>
       </c>
       <c r="F32">
-        <v>0.6887345541958698</v>
+        <v>0.6889228491124338</v>
       </c>
       <c r="G32">
-        <v>0.6960480111656706</v>
+        <v>0.6964035925163539</v>
       </c>
       <c r="H32">
-        <v>0.7062118776724273</v>
+        <v>0.7077767500089767</v>
       </c>
       <c r="I32">
-        <v>0.709713034817502</v>
+        <v>0.7118187606643449</v>
       </c>
       <c r="J32">
-        <v>0.7363622836172203</v>
+        <v>0.7431808669189185</v>
       </c>
       <c r="K32">
-        <v>0.7427841844724516</v>
+        <v>0.7503701524050619</v>
       </c>
       <c r="L32">
-        <v>0.757822860353172</v>
+        <v>0.7673365562319682</v>
       </c>
       <c r="M32">
-        <v>0.7662494642028771</v>
+        <v>0.7781592678344087</v>
       </c>
       <c r="N32">
-        <v>0.7767167953365317</v>
+        <v>0.7945010048580714</v>
       </c>
       <c r="O32">
-        <v>0.7866994273157979</v>
+        <v>0.8112410023459448</v>
       </c>
       <c r="P32">
-        <v>0.7921250303626941</v>
+        <v>0.817506386068773</v>
       </c>
       <c r="Q32">
-        <v>0.8076328324146124</v>
+        <v>0.8312356677261645</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.6178848867318328</v>
+        <v>0.6180592335406229</v>
       </c>
       <c r="D33">
-        <v>0.6610786094462839</v>
+        <v>0.66116444829425</v>
       </c>
       <c r="E33">
-        <v>0.6834860611700893</v>
+        <v>0.6838012519195112</v>
       </c>
       <c r="F33">
-        <v>0.6885893400912492</v>
+        <v>0.6888709840074104</v>
       </c>
       <c r="G33">
-        <v>0.695833622446561</v>
+        <v>0.6963204791949642</v>
       </c>
       <c r="H33">
-        <v>0.7055925712205507</v>
+        <v>0.7074913603255171</v>
       </c>
       <c r="I33">
-        <v>0.7089411430829455</v>
+        <v>0.7114491513952791</v>
       </c>
       <c r="J33">
-        <v>0.7349364769389461</v>
+        <v>0.7423612951787404</v>
       </c>
       <c r="K33">
-        <v>0.7415074642921033</v>
+        <v>0.7495453886269636</v>
       </c>
       <c r="L33">
-        <v>0.7568542498303981</v>
+        <v>0.7665749868376014</v>
       </c>
       <c r="M33">
-        <v>0.7649157545725253</v>
+        <v>0.7772216719199205</v>
       </c>
       <c r="N33">
-        <v>0.7749173248090728</v>
+        <v>0.7937793159931373</v>
       </c>
       <c r="O33">
-        <v>0.7835198925039324</v>
+        <v>0.8104287431268917</v>
       </c>
       <c r="P33">
-        <v>0.7882716410613257</v>
+        <v>0.8167861382579822</v>
       </c>
       <c r="Q33">
-        <v>0.8009491368097972</v>
+        <v>0.8308019003483891</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0.6178146309984232</v>
+        <v>0.6180310735987883</v>
       </c>
       <c r="D34">
-        <v>0.6610574173285608</v>
+        <v>0.6611521097597738</v>
       </c>
       <c r="E34">
-        <v>0.6833779493554066</v>
+        <v>0.6837308856743245</v>
       </c>
       <c r="F34">
-        <v>0.6885050392337422</v>
+        <v>0.6888038109726343</v>
       </c>
       <c r="G34">
-        <v>0.6957169276824462</v>
+        <v>0.6962044028996262</v>
       </c>
       <c r="H34">
-        <v>0.7052657659617585</v>
+        <v>0.7070722927604218</v>
       </c>
       <c r="I34">
-        <v>0.708541238120582</v>
+        <v>0.7108927045641135</v>
       </c>
       <c r="J34">
-        <v>0.7341999190195752</v>
+        <v>0.7408014526744857</v>
       </c>
       <c r="K34">
-        <v>0.7408773663386967</v>
+        <v>0.7477674868031832</v>
       </c>
       <c r="L34">
-        <v>0.7565936723959916</v>
+        <v>0.7637391426381358</v>
       </c>
       <c r="M34">
-        <v>0.7646208076536372</v>
+        <v>0.7734920332965789</v>
       </c>
       <c r="N34">
-        <v>0.7744324548962728</v>
+        <v>0.7884367946622814</v>
       </c>
       <c r="O34">
-        <v>0.7826804810354266</v>
+        <v>0.804048843885897</v>
       </c>
       <c r="P34">
-        <v>0.7873159526512181</v>
+        <v>0.8098402207905973</v>
       </c>
       <c r="Q34">
-        <v>0.7980438149125544</v>
+        <v>0.8236718459068502</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0.6176325889485793</v>
+        <v>0.617995194249328</v>
       </c>
       <c r="D35">
-        <v>0.6609981323144348</v>
+        <v>0.6611417899323763</v>
       </c>
       <c r="E35">
-        <v>0.6831351137334064</v>
+        <v>0.6836410818050516</v>
       </c>
       <c r="F35">
-        <v>0.6883233221319154</v>
+        <v>0.6887230346077483</v>
       </c>
       <c r="G35">
-        <v>0.6954741708434762</v>
+        <v>0.6960749758000186</v>
       </c>
       <c r="H35">
-        <v>0.7044678160203042</v>
+        <v>0.7066742281563816</v>
       </c>
       <c r="I35">
-        <v>0.707510463727157</v>
+        <v>0.7103690221384849</v>
       </c>
       <c r="J35">
-        <v>0.7315454497338227</v>
+        <v>0.7394452486860534</v>
       </c>
       <c r="K35">
-        <v>0.7382764610092023</v>
+        <v>0.7462042379762602</v>
       </c>
       <c r="L35">
-        <v>0.7541596523540838</v>
+        <v>0.7612108448963886</v>
       </c>
       <c r="M35">
-        <v>0.7622905377148462</v>
+        <v>0.770039119328475</v>
       </c>
       <c r="N35">
-        <v>0.7709882594654982</v>
+        <v>0.7832830265259871</v>
       </c>
       <c r="O35">
-        <v>0.7778701055902639</v>
+        <v>0.7965826135905658</v>
       </c>
       <c r="P35">
-        <v>0.7818142748581243</v>
+        <v>0.8013718017417313</v>
       </c>
       <c r="Q35">
-        <v>0.7889477468538194</v>
+        <v>0.8119303040251304</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.6180798884888821</v>
+        <v>0.6176374428783138</v>
       </c>
       <c r="D36">
-        <v>0.661174442282767</v>
+        <v>0.6610309869644317</v>
       </c>
       <c r="E36">
-        <v>0.6838510955361977</v>
+        <v>0.6830410955684432</v>
       </c>
       <c r="F36">
-        <v>0.6889228491124338</v>
+        <v>0.6882641874686758</v>
       </c>
       <c r="G36">
-        <v>0.6964035925163539</v>
+        <v>0.6954382226243554</v>
       </c>
       <c r="H36">
-        <v>0.7077767500089767</v>
+        <v>0.704601317694082</v>
       </c>
       <c r="I36">
-        <v>0.7118187606643449</v>
+        <v>0.7076719493595529</v>
       </c>
       <c r="J36">
-        <v>0.7431808669189185</v>
+        <v>0.7328392466161948</v>
       </c>
       <c r="K36">
-        <v>0.7503701524050619</v>
+        <v>0.7398914845152426</v>
       </c>
       <c r="L36">
-        <v>0.7673365562319682</v>
+        <v>0.7553611808501715</v>
       </c>
       <c r="M36">
-        <v>0.7781592678344087</v>
+        <v>0.7629851017662035</v>
       </c>
       <c r="N36">
-        <v>0.7945010048580714</v>
+        <v>0.7734014676482637</v>
       </c>
       <c r="O36">
-        <v>0.8112410023459448</v>
+        <v>0.7810384565266301</v>
       </c>
       <c r="P36">
-        <v>0.817506386068773</v>
+        <v>0.784842566190218</v>
       </c>
       <c r="Q36">
-        <v>0.8312356677261645</v>
+        <v>0.7916868678540425</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0.6180592335406229</v>
+        <v>0.6491293981171593</v>
       </c>
       <c r="D37">
-        <v>0.66116444829425</v>
+        <v>0.6726938100643867</v>
       </c>
       <c r="E37">
-        <v>0.6838012519195112</v>
+        <v>0.7138724559852694</v>
       </c>
       <c r="F37">
-        <v>0.6888709840074104</v>
+        <v>0.7330735681796979</v>
       </c>
       <c r="G37">
-        <v>0.6963204791949642</v>
+        <v>0.7641145701796569</v>
       </c>
       <c r="H37">
-        <v>0.7074913603255171</v>
+        <v>0.8050135970665708</v>
       </c>
       <c r="I37">
-        <v>0.7114491513952791</v>
+        <v>0.8312799512450997</v>
       </c>
       <c r="J37">
-        <v>0.7423612951787404</v>
+        <v>0.844798996076043</v>
       </c>
       <c r="K37">
-        <v>0.7495453886269636</v>
+        <v>0.8552680924950157</v>
       </c>
       <c r="L37">
-        <v>0.7665749868376014</v>
+        <v>0.867386202617997</v>
       </c>
       <c r="M37">
-        <v>0.7772216719199205</v>
+        <v>0.8786659602863093</v>
       </c>
       <c r="N37">
-        <v>0.7937793159931373</v>
+        <v>0.8873752875208518</v>
       </c>
       <c r="O37">
-        <v>0.8104287431268917</v>
+        <v>0.9006802935262573</v>
       </c>
       <c r="P37">
-        <v>0.8167861382579822</v>
+        <v>0.9084155037317208</v>
       </c>
       <c r="Q37">
-        <v>0.8308019003483891</v>
+        <v>0.9158862420280217</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0.6180310735987883</v>
+        <v>0.6472802226904981</v>
       </c>
       <c r="D38">
-        <v>0.6611521097597738</v>
+        <v>0.6663741688953713</v>
       </c>
       <c r="E38">
-        <v>0.6837308856743245</v>
+        <v>0.697702230969182</v>
       </c>
       <c r="F38">
-        <v>0.6888038109726343</v>
+        <v>0.7109358571589171</v>
       </c>
       <c r="G38">
-        <v>0.6962044028996262</v>
+        <v>0.723360917531636</v>
       </c>
       <c r="H38">
-        <v>0.7070722927604218</v>
+        <v>0.7396261355081913</v>
       </c>
       <c r="I38">
-        <v>0.7108927045641135</v>
+        <v>0.7539983296425135</v>
       </c>
       <c r="J38">
-        <v>0.7408014526744857</v>
+        <v>0.7792358700064386</v>
       </c>
       <c r="K38">
-        <v>0.7477674868031832</v>
+        <v>0.7947521245689063</v>
       </c>
       <c r="L38">
-        <v>0.7637391426381358</v>
+        <v>0.8287249317479332</v>
       </c>
       <c r="M38">
-        <v>0.7734920332965789</v>
+        <v>0.849121666411473</v>
       </c>
       <c r="N38">
-        <v>0.7884367946622814</v>
+        <v>0.8530308527280686</v>
       </c>
       <c r="O38">
-        <v>0.804048843885897</v>
+        <v>0.8677731712103081</v>
       </c>
       <c r="P38">
-        <v>0.8098402207905973</v>
+        <v>0.8766867149564259</v>
       </c>
       <c r="Q38">
-        <v>0.8236718459068502</v>
+        <v>0.8833651244186799</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0.617995194249328</v>
+        <v>0.6472287373179957</v>
       </c>
       <c r="D39">
-        <v>0.6611417899323763</v>
+        <v>0.6662561930641608</v>
       </c>
       <c r="E39">
-        <v>0.6836410818050516</v>
+        <v>0.6951197036800285</v>
       </c>
       <c r="F39">
-        <v>0.6887230346077483</v>
+        <v>0.7082661397085106</v>
       </c>
       <c r="G39">
-        <v>0.6960749758000186</v>
+        <v>0.7204592489087327</v>
       </c>
       <c r="H39">
-        <v>0.7066742281563816</v>
+        <v>0.7364241948925039</v>
       </c>
       <c r="I39">
-        <v>0.7103690221384849</v>
+        <v>0.7469732062341955</v>
       </c>
       <c r="J39">
-        <v>0.7394452486860534</v>
+        <v>0.7646449185916887</v>
       </c>
       <c r="K39">
-        <v>0.7462042379762602</v>
+        <v>0.7802541028556874</v>
       </c>
       <c r="L39">
-        <v>0.7612108448963886</v>
+        <v>0.8000112483524892</v>
       </c>
       <c r="M39">
-        <v>0.770039119328475</v>
+        <v>0.80700683213346</v>
       </c>
       <c r="N39">
-        <v>0.7832830265259871</v>
+        <v>0.827274343004009</v>
       </c>
       <c r="O39">
-        <v>0.7965826135905658</v>
+        <v>0.8401025460734068</v>
       </c>
       <c r="P39">
-        <v>0.8013718017417313</v>
+        <v>0.848624980571242</v>
       </c>
       <c r="Q39">
-        <v>0.8119303040251304</v>
+        <v>0.8612558416679517</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0.6176374428783138</v>
+        <v>0.619735203434455</v>
       </c>
       <c r="D40">
-        <v>0.6610309869644317</v>
+        <v>0.6333832928066546</v>
       </c>
       <c r="E40">
-        <v>0.6830410955684432</v>
+        <v>0.6787383133515561</v>
       </c>
       <c r="F40">
-        <v>0.6882641874686758</v>
+        <v>0.7124562340646758</v>
       </c>
       <c r="G40">
-        <v>0.6954382226243554</v>
+        <v>0.7496361943136062</v>
       </c>
       <c r="H40">
-        <v>0.704601317694082</v>
+        <v>0.7695284008053538</v>
       </c>
       <c r="I40">
-        <v>0.7076719493595529</v>
+        <v>0.7976390916157918</v>
       </c>
       <c r="J40">
-        <v>0.7328392466161948</v>
+        <v>0.8204771615311517</v>
       </c>
       <c r="K40">
-        <v>0.7398914845152426</v>
+        <v>0.8370226248867162</v>
       </c>
       <c r="L40">
-        <v>0.7553611808501715</v>
+        <v>0.848164293111459</v>
       </c>
       <c r="M40">
-        <v>0.7629851017662035</v>
+        <v>0.8611226525745019</v>
       </c>
       <c r="N40">
-        <v>0.7734014676482637</v>
+        <v>0.874107463704207</v>
       </c>
       <c r="O40">
-        <v>0.7810384565266301</v>
+        <v>0.8878957158863929</v>
       </c>
       <c r="P40">
-        <v>0.784842566190218</v>
+        <v>0.8982594701310169</v>
       </c>
       <c r="Q40">
-        <v>0.7916868678540425</v>
+        <v>0.9086657345150582</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.6491293981171593</v>
+        <v>0.6173773223053315</v>
       </c>
       <c r="D41">
-        <v>0.6726938100643867</v>
+        <v>0.6628752012978114</v>
       </c>
       <c r="E41">
-        <v>0.7138724559852694</v>
+        <v>0.7229838463206135</v>
       </c>
       <c r="F41">
-        <v>0.7330735681796979</v>
+        <v>0.7601420134698175</v>
       </c>
       <c r="G41">
-        <v>0.7641145701796569</v>
+        <v>0.7912858450045748</v>
       </c>
       <c r="H41">
-        <v>0.8050135970665708</v>
+        <v>0.8183358407599028</v>
       </c>
       <c r="I41">
-        <v>0.8312799512450997</v>
+        <v>0.8360150271944462</v>
       </c>
       <c r="J41">
-        <v>0.844798996076043</v>
+        <v>0.8472208098695676</v>
       </c>
       <c r="K41">
-        <v>0.8552680924950157</v>
+        <v>0.8625139580719926</v>
       </c>
       <c r="L41">
-        <v>0.867386202617997</v>
+        <v>0.8700905091512906</v>
       </c>
       <c r="M41">
-        <v>0.8786659602863093</v>
+        <v>0.888471474998785</v>
       </c>
       <c r="N41">
-        <v>0.8873752875208518</v>
+        <v>0.9070302450830061</v>
       </c>
       <c r="O41">
-        <v>0.9006802935262573</v>
+        <v>0.9182267021434549</v>
       </c>
       <c r="P41">
-        <v>0.9084155037317208</v>
+        <v>0.9278150153230389</v>
       </c>
       <c r="Q41">
-        <v>0.9158862420280217</v>
+        <v>0.9365466625774925</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.6472802226904981</v>
+        <v>0.5038544743145424</v>
       </c>
       <c r="D42">
-        <v>0.6663741688953713</v>
+        <v>0.6511762017213585</v>
       </c>
       <c r="E42">
-        <v>0.697702230969182</v>
+        <v>0.6744938819741688</v>
       </c>
       <c r="F42">
-        <v>0.7109358571589171</v>
+        <v>0.7216140036739931</v>
       </c>
       <c r="G42">
-        <v>0.723360917531636</v>
+        <v>0.751146005814281</v>
       </c>
       <c r="H42">
-        <v>0.7396261355081913</v>
+        <v>0.7658088206510554</v>
       </c>
       <c r="I42">
-        <v>0.7539983296425135</v>
+        <v>0.7826458849980422</v>
       </c>
       <c r="J42">
-        <v>0.7792358700064386</v>
+        <v>0.7947978155069327</v>
       </c>
       <c r="K42">
-        <v>0.7947521245689063</v>
+        <v>0.8287876589326277</v>
       </c>
       <c r="L42">
-        <v>0.8287249317479332</v>
+        <v>0.8484811224511225</v>
       </c>
       <c r="M42">
-        <v>0.849121666411473</v>
+        <v>0.864581405783565</v>
       </c>
       <c r="N42">
-        <v>0.8530308527280686</v>
+        <v>0.8933271136131946</v>
       </c>
       <c r="O42">
-        <v>0.8677731712103081</v>
+        <v>0.9007914603296567</v>
       </c>
       <c r="P42">
-        <v>0.8766867149564259</v>
+        <v>0.9094671571744516</v>
       </c>
       <c r="Q42">
-        <v>0.8833651244186799</v>
+        <v>0.9226142305883073</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0.6472287373179957</v>
+        <v>0.6355865009659161</v>
       </c>
       <c r="D43">
-        <v>0.6662561930641608</v>
+        <v>0.669414599609491</v>
       </c>
       <c r="E43">
-        <v>0.6951197036800285</v>
+        <v>0.7030182470801745</v>
       </c>
       <c r="F43">
-        <v>0.7082661397085106</v>
+        <v>0.7259403648356724</v>
       </c>
       <c r="G43">
-        <v>0.7204592489087327</v>
+        <v>0.7571791451578468</v>
       </c>
       <c r="H43">
-        <v>0.7364241948925039</v>
+        <v>0.7788414061450253</v>
       </c>
       <c r="I43">
-        <v>0.7469732062341955</v>
+        <v>0.8037869263306345</v>
       </c>
       <c r="J43">
-        <v>0.7646449185916887</v>
+        <v>0.8175071837806387</v>
       </c>
       <c r="K43">
-        <v>0.7802541028556874</v>
+        <v>0.8386567458185377</v>
       </c>
       <c r="L43">
-        <v>0.8000112483524892</v>
+        <v>0.8669944780684178</v>
       </c>
       <c r="M43">
-        <v>0.80700683213346</v>
+        <v>0.883769512092448</v>
       </c>
       <c r="N43">
-        <v>0.827274343004009</v>
+        <v>0.8975871751366885</v>
       </c>
       <c r="O43">
-        <v>0.8401025460734068</v>
+        <v>0.9090488446200516</v>
       </c>
       <c r="P43">
-        <v>0.848624980571242</v>
+        <v>0.9204252326123947</v>
       </c>
       <c r="Q43">
-        <v>0.8612558416679517</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
-        <v>0.619735203434455</v>
-      </c>
-      <c r="D44">
-        <v>0.6333832928066546</v>
-      </c>
-      <c r="E44">
-        <v>0.6787383133515561</v>
-      </c>
-      <c r="F44">
-        <v>0.7124562340646758</v>
-      </c>
-      <c r="G44">
-        <v>0.7496361943136062</v>
-      </c>
-      <c r="H44">
-        <v>0.7695284008053538</v>
-      </c>
-      <c r="I44">
-        <v>0.7976390916157918</v>
-      </c>
-      <c r="J44">
-        <v>0.8204771615311517</v>
-      </c>
-      <c r="K44">
-        <v>0.8370226248867162</v>
-      </c>
-      <c r="L44">
-        <v>0.848164293111459</v>
-      </c>
-      <c r="M44">
-        <v>0.8611226525745019</v>
-      </c>
-      <c r="N44">
-        <v>0.874107463704207</v>
-      </c>
-      <c r="O44">
-        <v>0.8878957158863929</v>
-      </c>
-      <c r="P44">
-        <v>0.8982594701310169</v>
-      </c>
-      <c r="Q44">
-        <v>0.9086657345150582</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45">
-        <v>0.6173773223053315</v>
-      </c>
-      <c r="D45">
-        <v>0.6628752012978114</v>
-      </c>
-      <c r="E45">
-        <v>0.7229838463206135</v>
-      </c>
-      <c r="F45">
-        <v>0.7601420134698175</v>
-      </c>
-      <c r="G45">
-        <v>0.7912858450045748</v>
-      </c>
-      <c r="H45">
-        <v>0.8183358407599028</v>
-      </c>
-      <c r="I45">
-        <v>0.8360150271944462</v>
-      </c>
-      <c r="J45">
-        <v>0.8472208098695676</v>
-      </c>
-      <c r="K45">
-        <v>0.8625139580719926</v>
-      </c>
-      <c r="L45">
-        <v>0.8700905091512906</v>
-      </c>
-      <c r="M45">
-        <v>0.888471474998785</v>
-      </c>
-      <c r="N45">
-        <v>0.9070302450830061</v>
-      </c>
-      <c r="O45">
-        <v>0.9182267021434549</v>
-      </c>
-      <c r="P45">
-        <v>0.9278150153230389</v>
-      </c>
-      <c r="Q45">
-        <v>0.9365466625774925</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
-        <v>0.5038544743145424</v>
-      </c>
-      <c r="D46">
-        <v>0.6511762017213585</v>
-      </c>
-      <c r="E46">
-        <v>0.6744938819741688</v>
-      </c>
-      <c r="F46">
-        <v>0.7216140036739931</v>
-      </c>
-      <c r="G46">
-        <v>0.751146005814281</v>
-      </c>
-      <c r="H46">
-        <v>0.7658088206510554</v>
-      </c>
-      <c r="I46">
-        <v>0.7826458849980422</v>
-      </c>
-      <c r="J46">
-        <v>0.7947978155069327</v>
-      </c>
-      <c r="K46">
-        <v>0.8287876589326277</v>
-      </c>
-      <c r="L46">
-        <v>0.8484811224511225</v>
-      </c>
-      <c r="M46">
-        <v>0.864581405783565</v>
-      </c>
-      <c r="N46">
-        <v>0.8933271136131946</v>
-      </c>
-      <c r="O46">
-        <v>0.9007914603296567</v>
-      </c>
-      <c r="P46">
-        <v>0.9094671571744516</v>
-      </c>
-      <c r="Q46">
-        <v>0.9226142305883073</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-      <c r="C47">
-        <v>0.6355865009659161</v>
-      </c>
-      <c r="D47">
-        <v>0.669414599609491</v>
-      </c>
-      <c r="E47">
-        <v>0.7030182470801745</v>
-      </c>
-      <c r="F47">
-        <v>0.7259403648356724</v>
-      </c>
-      <c r="G47">
-        <v>0.7571791451578468</v>
-      </c>
-      <c r="H47">
-        <v>0.7788414061450253</v>
-      </c>
-      <c r="I47">
-        <v>0.8037869263306345</v>
-      </c>
-      <c r="J47">
-        <v>0.8175071837806387</v>
-      </c>
-      <c r="K47">
-        <v>0.8386567458185377</v>
-      </c>
-      <c r="L47">
-        <v>0.8669944780684178</v>
-      </c>
-      <c r="M47">
-        <v>0.883769512092448</v>
-      </c>
-      <c r="N47">
-        <v>0.8975871751366885</v>
-      </c>
-      <c r="O47">
-        <v>0.9090488446200516</v>
-      </c>
-      <c r="P47">
-        <v>0.9204252326123947</v>
-      </c>
-      <c r="Q47">
         <v>0.9274162461382027</v>
       </c>
     </row>
